--- a/output/2026-10-04_14_Malesia_Pulau_Pinang_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-10-04_14_Malesia_Pulau_Pinang_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -474,7 +474,6 @@
           <t>Qbox Resources Sdn Bhd</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -490,10 +489,9 @@
           <t>604-584 4888 / 6012-548 7298</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore one-stop-shop di prodotti industriali: cleanroom, ESD, sicurezza/PPE. Sede: No. 16-02, Jalan Vervea 9, 14110 Bandar Cassia, Penang. Contatto: Chamby Toh (Director). Verificare se tratta anche linee affini a Dupuy. Fonte: investpenang.gov.my.</t>
+          <t>Distributore one-stop-shop di prodotti industriali: cleanroom, ESD, sicurezza/PPE. Sede: No. 16-02, Jalan Vervea 9, 14110 Bandar Cassia, Penang. Contatto: Chamby Toh (Director). Verificare se tratta anche linee affini a Dupuy. Fonte: investpenang.gov.my. [DUPLICATO — vedi anche: 2026-10-03_20_Malesia_Pulau_Pinang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -535,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore di strumenti di misura, leak detection, prodotti per vuoto, power tools e forniture industriali. Sede: Bayan Lepas, Penang. Contatto: Edwin Chong. Fonte: investpenang.gov.my.</t>
+          <t>Distributore di strumenti di misura, leak detection, prodotti per vuoto, power tools e forniture industriali. Sede: Bayan Lepas, Penang. Contatto: Edwin Chong. Fonte: investpenang.gov.my. [DUPLICATO — vedi anche: 2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -550,7 +548,6 @@
           <t>Berjaya Hardware (B'Worth) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -561,11 +558,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dal 1983, fornitore di hardware industriale/macchinari e utensili automotive/engineering a Butterworth, Penang. Fonte: investpenang.gov.my.</t>
+          <t>Dal 1983, fornitore di hardware industriale/macchinari e utensili automotive/engineering a Butterworth, Penang. Fonte: investpenang.gov.my. [DUPLICATO — vedi anche: 2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -580,7 +575,6 @@
           <t>Textran Industries (Penang) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -591,11 +585,9 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore/stockist di fasteners e hardware elettromeccanico dal 1998, Bukit Mertajam, Penang. CEO: Tan Bak Soon. Fonte: investpenang.gov.my, sme100.asia.</t>
+          <t>Distributore/stockist di fasteners e hardware elettromeccanico dal 1998, Bukit Mertajam, Penang. CEO: Tan Bak Soon. Fonte: investpenang.gov.my, sme100.asia. [DUPLICATO — vedi anche: 2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -630,10 +622,9 @@
           <t>+604 380 1277/78; +6012-528 2779 (WhatsApp)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dal 2006, fornitore/distributore di componenti pneumatici e hardware a Perai, Penang; dal 2015 offre anche servizi di metal fabrication/precision machining (attivita' mista: verificare prevalenza distributiva). Fonte: sito aziendale, jobstore.my.</t>
+          <t>Dal 2006, fornitore/distributore di componenti pneumatici e hardware a Perai, Penang; dal 2015 offre anche servizi di metal fabrication/precision machining (attivita' mista: verificare prevalenza distributiva). Fonte: sito aziendale, jobstore.my. [DUPLICATO — vedi anche: 2026-10-04_00_Malesia_Pulau_Pinang_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -648,7 +639,6 @@
           <t>Dynarco Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -659,8 +649,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Dal 1986, fornitore/rivenditore di macchinari per l'industria della lavorazione di precisione (rettificatrici, fresatrici, EDM, torni, centri CNC, accessori) a Perai, Penang. Rivenditore di macchine utensili verso officine terze, non un'officina conto terzi. Fonte: jobstore.my, machinetools.com, investpenang.gov.my.</t>
@@ -668,7 +656,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -678,7 +666,6 @@
           <t>Fastenal Malaysia Sdn Bhd (filiale Penang)</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -689,8 +676,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Filiale malese del distributore globale Fastenal (fasteners, utensili, forniture industriali), sede a Simpang Ampat, Penang (No.1034A, Jalan Kebun Baru, Kawasan Perindustrian Ringan Juru). Fonte: jobstore.my, maukerja.my, careerconnect.mmu.edu.my.</t>
@@ -698,7 +683,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -728,10 +713,9 @@
           <t>+603 7728 6250 (sede HQ Petaling Jaya)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Channel partner/distributore di prodotti elettrici esplosion-proof ATEX (Ceag, Rittal, Mennekes, Mankenberg). Sede principale a Petaling Jaya, Selangor; ufficio vendita locale a Penang confermato senza recapito diretto separato. Fonte: malaysia.ahk.de (AHK Malaysia-Germany Chamber).</t>
+          <t>Channel partner/distributore di prodotti elettrici esplosion-proof ATEX (Ceag, Rittal, Mennekes, Mankenberg). Sede principale a Petaling Jaya, Selangor; ufficio vendita locale a Penang confermato senza recapito diretto separato. Fonte: malaysia.ahk.de (AHK Malaysia-Germany Chamber). [DUPLICATO — vedi anche: 2026-10-02_18_Malesia_Negeri_Sembilan_ATEX_Equipment_Services.xlsx]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -746,7 +730,6 @@
           <t>MaxMega Malaysia (ufficio Penang)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -757,8 +740,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Ufficio/rappresentante locale a Penang (22D Jalan Tun Dr. Awang, 11900 Penang) per prodotti aree pericolose ATEX &amp; IECEx (sensori di livello Deeter Electronics). Telefono/email specifici non reperiti. Fonte: deeterelectronics.com/sales-reps/maxmega-malaysia-penang-office/.</t>
@@ -776,7 +757,6 @@
           <t>JetCan Engineering Sdn Bhd</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -787,8 +767,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Vendita/assistenza equipaggiamento aria compressa e accessori, sede a Penang (Malesia del nord), focus food &amp; beverage, E&amp;E, medical devices. Dal nov 2024/gen 2025 acquisita e integrata in Atlas Copco Group (Compressor Technique Business Area): verificare se opera ancora come distributore multi-brand indipendente. Fonte: atlascopcogroup.com press releases.</t>
@@ -821,7 +799,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>acumen.wong@gmail.com (email personale, non dominio aziendale: verificare)</t>
@@ -844,7 +821,6 @@
           <t>ASB Welding Machinery Sdn Bhd</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Pulau Pinang</t>
@@ -855,8 +831,6 @@
           <t>Metalworking / Lavorazioni Metalliche</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Fornitore di macchinari per saldatura a Bukit Mertajam, Penang (No.11, Jalan Industri Permatang Batu). Vende macchine/attrezzature a terzi, non e' un'officina conto terzi. Esistenza confermata da inserzioni di lavoro su maukerja.my. Fonte: maukerja.my, rentechdigital.</t>
@@ -864,7 +838,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
